--- a/etc/hebrew/phrases.xlsx
+++ b/etc/hebrew/phrases.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -689,6 +689,69 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>recently; lately</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>בַּזְּמַן הָאַחֲרוֹן</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>nothing; not anything</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>שׁוּם דָּבָר</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>good luck</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>בְּהַצְלָחָה</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/phrases.xlsx
+++ b/etc/hebrew/phrases.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -752,6 +752,27 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>plus; and more</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>וְעוֹד</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>math operator / phrase</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/phrases.xlsx
+++ b/etc/hebrew/phrases.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -773,6 +773,48 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>thank you very much</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>תּוֹדָה רַבָּה</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>we have</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>יֵשׁ לָנוּ</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/phrases.xlsx
+++ b/etc/hebrew/phrases.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -815,6 +815,174 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>soon</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>עוֹד מְעַט</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>phrase; adverbial</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>abroad</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>חוּץ לָאָרֶץ</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>phrase; abbreviation: חו״ל</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>מֶזֶג הָאֲוִיר</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>noun phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>afterwards; after that</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>אַחַר כָּךְ</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>phrase; adverbial</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>everything; anything</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>כָּל דָּבָר</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>fruit and vegetable shop</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>חֲנוּת פֵּרוֹת וִירָקוֹת</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>electronics shop</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>חֲנוּת אֶלֶקְטְרוֹנִיקָה</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>please</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>בְּבַקָּשָׁה</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/phrases.xlsx
+++ b/etc/hebrew/phrases.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -983,6 +983,111 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>יוֹם הֻלֶּדֶת</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>phrase; event noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>once upon a time</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>הָיֹה הָיָה פַּעַם</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>by chance; in case</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>בְּמִקְרֶה</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>phrase; adverbial</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>most of all</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>הֲכִי הֲכִי הַרְבֵּה</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>garden strawberry</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>תּוּת גִּנָּה</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>phrase; plant/food noun</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
